--- a/docs/import-template.xlsx
+++ b/docs/import-template.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
   <si>
     <t>Date</t>
   </si>
@@ -32,9 +32,6 @@
     <t>Note</t>
   </si>
   <si>
-    <t>Resume Link</t>
-  </si>
-  <si>
     <t>2026-08-24</t>
   </si>
   <si>
@@ -53,9 +50,6 @@
     <t>Referred by a friend</t>
   </si>
   <si>
-    <t>https://drive.example.com/resume-backend.pdf</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -116,10 +110,7 @@
     <t>Note          free text.</t>
   </si>
   <si>
-    <t>Resume Link   any URL.</t>
-  </si>
-  <si>
-    <t>Header names are matched loosely: "Job URL", "Link", "Company", "Notes", "CV" and similar all work.</t>
+    <t>Header names are matched loosely: "Job URL", "Link", "Company", "Notes" and similar variants all work.</t>
   </si>
   <si>
     <t>Column order does not matter. Extra columns are ignored.</t>
@@ -525,7 +516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" style="1" customWidth="1"/>
@@ -534,10 +525,9 @@
     <col min="4" max="4" width="62" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="42" customWidth="1"/>
-    <col min="7" max="7" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -556,100 +546,85 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="B4" t="s">
         <v>16</v>
       </c>
-      <c r="G3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
         <v>20</v>
       </c>
-      <c r="E4" t="s">
+      <c r="C5" t="s">
         <v>21</v>
       </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
         <v>22</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>23</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>24</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -660,7 +635,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -668,82 +643,77 @@
   <sheetData>
     <row r="1" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:1" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:1" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:1" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
